--- a/testdata/realdata/otn_ochs.xlsx
+++ b/testdata/realdata/otn_ochs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>占用纤芯</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +484,11 @@
           <t>OC-HDQ|1</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,6 +521,11 @@
           <t>OC-HDQ|2</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +558,11 @@
           <t>OC-HM|1</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -575,6 +595,11 @@
           <t>OC-HM|2</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,6 +632,11 @@
           <t>OC-HJ|1</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -639,6 +669,11 @@
           <t>OC-HJ|2</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -671,6 +706,11 @@
           <t>OC-JM|1</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -703,6 +743,11 @@
           <t>OC-JM|2</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -735,6 +780,11 @@
           <t>OC-QJ|1</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -767,6 +817,11 @@
           <t>OC-QJ|2</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +854,11 @@
           <t>OC-JM2|1</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -831,6 +891,11 @@
           <t>OC-JM2|2</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -863,6 +928,11 @@
           <t>OC-HY|1</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -893,6 +963,11 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>OC-HY|2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>
